--- a/samples/field_input_template.xlsx
+++ b/samples/field_input_template.xlsx
@@ -121,7 +121,7 @@
     <t>Normal concrete curing</t>
   </si>
   <si>
-    <t>architecture</t>
+    <t>건축</t>
   </si>
   <si>
     <t>1F</t>
@@ -139,7 +139,7 @@
     <t>Delayed rebar assembly</t>
   </si>
   <si>
-    <t>civil</t>
+    <t>토목</t>
   </si>
   <si>
     <t>B1</t>
@@ -169,7 +169,7 @@
     <t>MEP ceiling framing cost overrun</t>
   </si>
   <si>
-    <t>mechanical</t>
+    <t>기계설비</t>
   </si>
   <si>
     <t>2F</t>
@@ -184,7 +184,7 @@
     <t>Fire pump delivery delay</t>
   </si>
   <si>
-    <t>fire_protection</t>
+    <t>소방설비</t>
   </si>
   <si>
     <t>Machine Room</t>
@@ -199,7 +199,7 @@
     <t>Electrical panel inspection delay</t>
   </si>
   <si>
-    <t>electrical</t>
+    <t>전기설비</t>
   </si>
   <si>
     <t>EPS</t>

--- a/samples/field_input_template.xlsx
+++ b/samples/field_input_template.xlsx
@@ -15,6 +15,11 @@
     <sheet name="06_부진공정" sheetId="6" r:id="rId6"/>
     <sheet name="07_보고서" sheetId="7" r:id="rId7"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'01_실적입력'!$A$3:$H$9</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'02_원가입력'!$A$3:$F$9</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'03_자재검측'!$A$3:$H$9</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -335,7 +340,9 @@
   <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
@@ -632,8 +639,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
   <dimension ref="A1:H9"/>
   <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="8" width="18.7109375" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:8">
       <c r="A1" s="1" t="s">
@@ -742,14 +755,31 @@
       <c r="H9" s="2"/>
     </row>
   </sheetData>
+  <sheetProtection sheet="1" objects="1" scenarios="1"/>
+  <autoFilter ref="A3:H9"/>
+  <dataValidations count="2">
+    <dataValidation type="date" operator="greaterThanOrEqual" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B4:B201">
+      <formula1>2020-01-01</formula1>
+    </dataValidation>
+    <dataValidation type="decimal" operator="greaterThanOrEqual" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C4:E201">
+      <formula1>0</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup fitToHeight="0" orientation="landscape"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
   <dimension ref="A1:F9"/>
   <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="6" width="18.7109375" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" s="1" t="s">
@@ -840,14 +870,23 @@
       <c r="F9" s="2"/>
     </row>
   </sheetData>
+  <sheetProtection sheet="1" objects="1" scenarios="1"/>
+  <autoFilter ref="A3:F9"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup fitToHeight="0" orientation="landscape"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
   <dimension ref="A1:H9"/>
   <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="8" width="18.7109375" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:8">
       <c r="A1" s="1" t="s">
@@ -956,7 +995,15 @@
       <c r="H9" s="2"/>
     </row>
   </sheetData>
+  <sheetProtection sheet="1" objects="1" scenarios="1"/>
+  <autoFilter ref="A3:H9"/>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H4:H201">
+      <formula1>"planned,ordered,pending,delivered,approved,delayed"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup fitToHeight="0" orientation="landscape"/>
 </worksheet>
 </file>
 
@@ -1135,6 +1182,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:B8"/>
   <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="2" width="24.7109375" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="3" t="s">
